--- a/objects/recent_cancer_type.xlsx
+++ b/objects/recent_cancer_type.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -25,6 +25,9 @@
     <t xml:space="preserve">term</t>
   </si>
   <si>
+    <t xml:space="preserve">Severe COVID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitalized</t>
   </si>
   <si>
@@ -40,301 +43,382 @@
     <t xml:space="preserve">Breast cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58 (1.12, 2.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01 (1.17, 3.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93 (2.28, 6.77)</t>
+    <t xml:space="preserve">1.77 (1.30, 2.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65 (1.20, 2.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01 (1.20, 3.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76 (2.23, 6.35)</t>
   </si>
   <si>
     <t xml:space="preserve">unadjusted_firth</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60 (1.12, 2.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08 (1.17, 3.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06 (2.27, 6.68)</t>
+    <t xml:space="preserve">1.78 (1.30, 2.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67 (1.20, 2.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07 (1.19, 3.34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88 (2.22, 6.27)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27 (0.88, 1.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95 (1.08, 3.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63 (1.45, 4.42)</t>
+    <t xml:space="preserve">1.35 (0.98, 1.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32 (0.94, 1.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96 (1.12, 3.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44 (1.37, 4.02)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27 (0.85, 1.83)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15 (1.19, 3.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85 (1.53, 4.91)</t>
+    <t xml:space="preserve">1.34 (0.94, 1.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36 (0.94, 1.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13 (1.18, 3.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32 (1.22, 4.03)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39 (0.90, 2.07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91 (1.53, 5.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28 (1.66, 5.89)</t>
+    <t xml:space="preserve">1.41 (0.97, 2.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43 (0.96, 2.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76 (1.46, 4.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70 (1.38, 4.82)</t>
   </si>
   <si>
     <t xml:space="preserve">Hematologic malignancy</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41 (2.82, 4.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78 (2.00, 3.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43 (3.87, 7.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42 (2.82, 4.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81 (1.99, 3.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49 (3.87, 7.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47 (2.02, 2.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95 (1.37, 2.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06 (2.13, 4.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50 (2.02, 3.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93 (1.32, 2.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91 (1.96, 4.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45 (1.95, 3.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36 (1.57, 3.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65 (1.71, 3.97)</t>
+    <t xml:space="preserve">3.65 (3.10, 4.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35 (2.81, 3.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84 (2.08, 3.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05 (3.66, 6.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66 (3.09, 4.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86 (2.07, 3.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10 (3.65, 6.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67 (2.24, 3.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48 (2.06, 2.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03 (1.46, 2.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95 (2.08, 4.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65 (2.19, 3.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48 (2.04, 3.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97 (1.38, 2.74)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61 (1.78, 3.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56 (2.09, 3.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41 (1.95, 2.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36 (1.61, 3.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33 (1.52, 3.44)</t>
   </si>
   <si>
     <t xml:space="preserve">Lung cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69 (2.58, 5.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06 (1.65, 5.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93 (5.30, 15.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72 (2.58, 5.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18 (1.65, 5.54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17 (5.28, 14.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98 (1.36, 2.81)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68 (0.86, 2.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31 (1.88, 5.47)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92 (1.27, 2.81)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (0.71, 2.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95 (0.93, 3.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15 (1.41, 3.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95 (0.89, 3.74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13 (0.96, 4.12)</t>
+    <t xml:space="preserve">4.34 (3.17, 5.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49 (2.48, 4.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92 (1.59, 5.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81 (6.08, 15.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37 (3.17, 5.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52 (2.48, 4.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04 (1.58, 5.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.04 (6.06, 15.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16 (1.55, 2.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81 (1.27, 2.54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54 (0.80, 2.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57 (2.13, 5.66)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90 (1.30, 2.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77 (1.18, 2.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (0.72, 2.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50 (1.31, 4.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04 (1.38, 2.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91 (1.26, 2.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89 (0.86, 3.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70 (1.37, 4.84)</t>
   </si>
   <si>
     <t xml:space="preserve">Melanoma</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65 (2.10, 3.36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91 (1.21, 3.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70 (3.11, 7.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67 (2.10, 3.35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95 (1.21, 2.97)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78 (3.10, 7.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62 (1.27, 2.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21 (0.75, 1.86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93 (1.24, 2.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68 (1.28, 2.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16 (0.67, 1.86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24 (1.42, 3.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86 (1.41, 2.42)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55 (0.89, 2.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 (1.56, 3.79)</t>
+    <t xml:space="preserve">2.70 (2.18, 3.34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57 (2.06, 3.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87 (1.20, 2.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07 (3.48, 7.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71 (2.18, 3.34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58 (2.06, 3.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91 (1.20, 2.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15 (3.47, 7.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56 (1.25, 1.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57 (1.24, 1.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18 (0.74, 1.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03 (1.35, 2.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65 (1.30, 2.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63 (1.27, 2.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23 (0.74, 1.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32 (1.53, 3.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78 (1.39, 2.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78 (1.37, 2.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63 (0.97, 2.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51 (1.65, 3.69)</t>
   </si>
   <si>
     <t xml:space="preserve">Other cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98 (1.74, 2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64 (1.28, 2.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79 (2.14, 3.65)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98 (1.73, 2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65 (1.28, 2.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81 (2.14, 3.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35 (1.18, 1.55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14 (0.88, 1.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45 (1.09, 1.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40 (1.21, 1.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12 (0.85, 1.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35 (0.99, 1.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53 (1.32, 1.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47 (1.10, 1.93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50 (1.09, 2.02)</t>
+    <t xml:space="preserve">2.13 (1.89, 2.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02 (1.78, 2.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64 (1.30, 2.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83 (2.20, 3.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65 (1.30, 2.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84 (2.20, 3.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40 (1.24, 1.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37 (1.21, 1.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (0.89, 1.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46 (1.12, 1.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38 (1.21, 1.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38 (1.20, 1.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08 (0.83, 1.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24 (0.92, 1.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46 (1.27, 1.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (1.29, 1.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42 (1.07, 1.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34 (0.98, 1.78)</t>
   </si>
   <si>
     <t xml:space="preserve">Prostate cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98 (1.45, 2.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35 (0.72, 2.55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30 (2.58, 7.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00 (1.45, 2.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42 (0.72, 2.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43 (2.57, 7.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74 (0.53, 1.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47 (0.24, 0.84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00 (0.57, 1.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69 (0.47, 0.98)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53 (0.25, 0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15 (0.65, 1.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79 (0.52, 1.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61 (0.25, 1.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48 (0.81, 2.50)</t>
+    <t xml:space="preserve">2.33 (1.78, 3.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94 (1.44, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42 (0.78, 2.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66 (2.92, 7.45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34 (1.78, 3.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96 (1.44, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48 (0.77, 2.54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77 (2.91, 7.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83 (0.63, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74 (0.54, 0.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50 (0.26, 0.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09 (0.66, 1.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82 (0.60, 1.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71 (0.50, 0.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56 (0.28, 0.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15 (0.67, 1.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97 (0.69, 1.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81 (0.54, 1.15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66 (0.29, 1.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44 (0.82, 2.37)</t>
   </si>
 </sst>
 </file>
@@ -679,90 +763,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -792,90 +894,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -905,90 +1025,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>71</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1018,90 +1156,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>88</v>
+      </c>
+      <c r="F5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>92</v>
+      </c>
+      <c r="F6" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1131,90 +1287,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>97</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>99</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>103</v>
+      </c>
+      <c r="F4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>107</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>111</v>
+      </c>
+      <c r="F6" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1244,90 +1418,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>116</v>
+      </c>
+      <c r="F2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>120</v>
+      </c>
+      <c r="F3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>124</v>
+      </c>
+      <c r="F4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>128</v>
+      </c>
+      <c r="F5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>132</v>
+      </c>
+      <c r="F6" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/objects/recent_cancer_type.xlsx
+++ b/objects/recent_cancer_type.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35 (0.98, 1.82)</t>
+    <t xml:space="preserve">1.35 (0.98, 1.83)</t>
   </si>
   <si>
     <t xml:space="preserve">1.32 (0.94, 1.81)</t>
@@ -103,16 +103,16 @@
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41 (0.97, 2.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43 (0.96, 2.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76 (1.46, 4.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70 (1.38, 4.82)</t>
+    <t xml:space="preserve">1.42 (0.97, 2.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43 (0.96, 2.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76 (1.46, 4.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71 (1.38, 4.82)</t>
   </si>
   <si>
     <t xml:space="preserve">Hematologic malignancy</t>
@@ -139,37 +139,37 @@
     <t xml:space="preserve">5.10 (3.65, 6.95)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67 (2.24, 3.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 (2.06, 2.96)</t>
+    <t xml:space="preserve">2.67 (2.24, 3.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48 (2.07, 2.96)</t>
   </si>
   <si>
     <t xml:space="preserve">2.03 (1.46, 2.75)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95 (2.08, 4.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65 (2.19, 3.18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 (2.04, 3.01)</t>
+    <t xml:space="preserve">2.94 (2.08, 4.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65 (2.19, 3.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49 (2.04, 3.02)</t>
   </si>
   <si>
     <t xml:space="preserve">1.97 (1.38, 2.74)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61 (1.78, 3.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56 (2.09, 3.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41 (1.95, 2.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36 (1.61, 3.36)</t>
+    <t xml:space="preserve">2.62 (1.78, 3.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56 (2.09, 3.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40 (1.95, 2.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37 (1.61, 3.36)</t>
   </si>
   <si>
     <t xml:space="preserve">2.33 (1.52, 3.44)</t>
@@ -202,25 +202,25 @@
     <t xml:space="preserve">10.04 (6.06, 15.71)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16 (1.55, 2.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81 (1.27, 2.54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54 (0.80, 2.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57 (2.13, 5.66)</t>
+    <t xml:space="preserve">2.17 (1.56, 2.97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83 (1.27, 2.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54 (0.79, 2.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56 (2.12, 5.65)</t>
   </si>
   <si>
     <t xml:space="preserve">1.90 (1.30, 2.71)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77 (1.18, 2.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (0.72, 2.76)</t>
+    <t xml:space="preserve">1.77 (1.19, 2.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (0.71, 2.76)</t>
   </si>
   <si>
     <t xml:space="preserve">2.50 (1.31, 4.37)</t>
@@ -232,7 +232,7 @@
     <t xml:space="preserve">1.91 (1.26, 2.81)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89 (0.86, 3.61)</t>
+    <t xml:space="preserve">1.89 (0.87, 3.61)</t>
   </si>
   <si>
     <t xml:space="preserve">2.70 (1.37, 4.84)</t>
@@ -265,22 +265,22 @@
     <t xml:space="preserve">5.15 (3.47, 7.36)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56 (1.25, 1.93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57 (1.24, 1.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18 (0.74, 1.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03 (1.35, 2.94)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65 (1.30, 2.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63 (1.27, 2.08)</t>
+    <t xml:space="preserve">1.55 (1.24, 1.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56 (1.23, 1.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19 (0.74, 1.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04 (1.36, 2.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64 (1.29, 2.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62 (1.26, 2.06)</t>
   </si>
   <si>
     <t xml:space="preserve">1.23 (0.74, 1.92)</t>
@@ -289,16 +289,16 @@
     <t xml:space="preserve">2.32 (1.53, 3.38)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78 (1.39, 2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78 (1.37, 2.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63 (0.97, 2.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51 (1.65, 3.69)</t>
+    <t xml:space="preserve">1.77 (1.38, 2.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77 (1.36, 2.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62 (0.97, 2.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50 (1.64, 3.68)</t>
   </si>
   <si>
     <t xml:space="preserve">Other cancer</t>
@@ -322,40 +322,40 @@
     <t xml:space="preserve">2.84 (2.20, 3.62)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40 (1.24, 1.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37 (1.21, 1.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13 (0.89, 1.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46 (1.12, 1.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38 (1.21, 1.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38 (1.20, 1.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08 (0.83, 1.40)</t>
+    <t xml:space="preserve">1.41 (1.25, 1.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38 (1.22, 1.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (0.88, 1.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45 (1.12, 1.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39 (1.21, 1.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39 (1.21, 1.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08 (0.83, 1.39)</t>
   </si>
   <si>
     <t xml:space="preserve">1.24 (0.92, 1.64)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46 (1.27, 1.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (1.29, 1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42 (1.07, 1.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34 (0.98, 1.78)</t>
+    <t xml:space="preserve">1.47 (1.28, 1.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50 (1.30, 1.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43 (1.08, 1.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34 (0.99, 1.79)</t>
   </si>
   <si>
     <t xml:space="preserve">Prostate cancer</t>
@@ -385,7 +385,7 @@
     <t xml:space="preserve">4.77 (2.91, 7.38)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83 (0.63, 1.09)</t>
+    <t xml:space="preserve">0.84 (0.63, 1.09)</t>
   </si>
   <si>
     <t xml:space="preserve">0.74 (0.54, 0.99)</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">1.09 (0.66, 1.71)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.82 (0.60, 1.11)</t>
+    <t xml:space="preserve">0.83 (0.60, 1.11)</t>
   </si>
   <si>
     <t xml:space="preserve">0.71 (0.50, 0.98)</t>
@@ -412,7 +412,7 @@
     <t xml:space="preserve">0.97 (0.69, 1.33)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81 (0.54, 1.15)</t>
+    <t xml:space="preserve">0.80 (0.54, 1.15)</t>
   </si>
   <si>
     <t xml:space="preserve">0.66 (0.29, 1.29)</t>
